--- a/Dissertation Research/Reading List.xlsx
+++ b/Dissertation Research/Reading List.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -16,6 +16,7 @@
     <sheet name="Sheet3" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Schwarzbuch" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Common German" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Sheet9" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="527">
   <si>
     <t xml:space="preserve">History</t>
   </si>
@@ -38,6 +39,9 @@
     <t xml:space="preserve">Other</t>
   </si>
   <si>
+    <t xml:space="preserve">Spanish</t>
+  </si>
+  <si>
     <t xml:space="preserve">Polanyi</t>
   </si>
   <si>
@@ -56,6 +60,9 @@
     <t xml:space="preserve">Counterrevolution</t>
   </si>
   <si>
+    <t xml:space="preserve">Mariategui</t>
+  </si>
+  <si>
     <t xml:space="preserve">Braudel</t>
   </si>
   <si>
@@ -68,12 +75,18 @@
     <t xml:space="preserve">For Marx</t>
   </si>
   <si>
+    <t xml:space="preserve">Andreu Nin</t>
+  </si>
+  <si>
     <t xml:space="preserve">The Mediterranean II</t>
   </si>
   <si>
     <t xml:space="preserve">Reading Capital</t>
   </si>
   <si>
+    <t xml:space="preserve">Zapatistas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cox</t>
   </si>
   <si>
@@ -246,6 +259,12 @@
   </si>
   <si>
     <t xml:space="preserve">Essays on Marx's Theory of Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Origins of Capitalism</t>
   </si>
   <si>
     <t xml:space="preserve">Three essays on Marx's Value Theory</t>
@@ -1402,6 +1421,225 @@
   </si>
   <si>
     <t xml:space="preserve">sogar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chapter 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lichtenstein &amp; Meyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">On The Line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aglietta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theory of Capitalist Regulation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harvey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condition of Post-Modernity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vol 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age of Extremes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arrighi</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Long 20</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Century</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ford</t>
+  </si>
+  <si>
+    <t xml:space="preserve">My Life and Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gramsci</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fordism and Americanism</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chapter 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vogel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marxism and the Oppression of Women</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bhatacharya et al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Social Reproduction Theory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Households in the World Economy 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Households in the World Economy 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital Vol 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Five Dollar Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reproduction of Capital</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Peru Chapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devil and Mr Casement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siete Ensayos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valcarcel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Defense of the Caucheros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slavery in Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casement Reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Despues del Caucho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Perfiles Históricos de la Amazonía Peruana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Imaginario e imágenes de la época del caucho-Los sucesos del Putumayo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia Economica del Oriente Peruana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gran Bretana y el Peru</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil Chapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grandin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fordlandia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mike Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Late Victorian Holocausts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Barham and Coomes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prosperity’s Promise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weinstein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Amazon Rubber Boom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bunker and Ciccantel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Globalization and the Race for Resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brazil and the Struggle for Rubber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Malaya Chapter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crossing the Bay of Bengal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taming the Coolie Beast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footloose Labour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Women and Labour in Late Colonial India </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tentacles of Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Question of Class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colonial Labour Policy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">South Indians on the Plantation Frontier in Malaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fleeting Agencies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christopher Baker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An Indian Rural Economy 1880-1955</t>
   </si>
 </sst>
 </file>
@@ -1411,7 +1649,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1437,6 +1675,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
@@ -1549,12 +1795,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1567,10 +1817,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1632,6 +1878,10 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1884,7 +2134,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="5"/>
@@ -1892,7 +2142,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="43.33"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="45.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="0" width="10.16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16383" style="1" width="10.16"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1902,34 +2152,40 @@
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="3" t="n">
         <v>1944</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="C2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="5" t="n">
         <v>268</v>
       </c>
-      <c r="G2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="5" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>8</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1937,10 +2193,10 @@
         <v>1949</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>642</v>
@@ -1948,11 +2204,14 @@
       <c r="F3" s="1" t="n">
         <v>1965</v>
       </c>
-      <c r="G3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>12</v>
+      <c r="G3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1960,30 +2219,33 @@
         <v>1949</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>725</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>14</v>
+        <v>17</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="n">
         <v>1959</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>16</v>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>483</v>
@@ -1991,11 +2253,11 @@
       <c r="F5" s="1" t="n">
         <v>1966</v>
       </c>
-      <c r="G5" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>18</v>
+      <c r="G5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2003,10 +2265,10 @@
         <v>1962</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>368</v>
@@ -2014,22 +2276,22 @@
       <c r="F6" s="1" t="n">
         <v>1922</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>22</v>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="n">
         <v>1963</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>24</v>
+      <c r="B7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>864</v>
@@ -2037,11 +2299,11 @@
       <c r="F7" s="1" t="n">
         <v>1978</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>25</v>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2049,10 +2311,10 @@
         <v>1975</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D8" s="8" t="n">
         <v>354</v>
@@ -2060,11 +2322,11 @@
       <c r="F8" s="1" t="n">
         <v>1988</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>28</v>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2072,10 +2334,10 @@
         <v>1987</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9" s="13" t="n">
         <v>404</v>
@@ -2083,91 +2345,91 @@
       <c r="F9" s="1" t="n">
         <v>1990</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>31</v>
+      <c r="G9" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="n">
         <v>1967</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>32</v>
+      <c r="B10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>623</v>
       </c>
-      <c r="G10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>34</v>
+      <c r="G10" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="n">
         <v>1979</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>35</v>
+      <c r="B11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>670</v>
       </c>
-      <c r="G11" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" s="5" t="s">
-        <v>37</v>
+      <c r="G11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="n">
         <v>1979</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>38</v>
+      <c r="B12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>42</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>699</v>
       </c>
-      <c r="G12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="5" t="s">
-        <v>39</v>
+      <c r="G12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="n">
         <v>1971</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>41</v>
+      <c r="B13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="G13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>43</v>
+      <c r="G13" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2175,19 +2437,19 @@
         <v>1972</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" s="15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" s="16" t="n">
         <v>312</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2195,50 +2457,50 @@
         <v>1974</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" s="19" t="n">
         <v>440</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="n">
         <v>1980</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>51</v>
+      <c r="B16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D16" s="10" t="n">
         <v>397</v>
       </c>
-      <c r="G16" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="5" t="s">
-        <v>53</v>
+      <c r="G16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="n">
         <v>1988</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>55</v>
+      <c r="B17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>59</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>434</v>
@@ -2246,28 +2508,28 @@
       <c r="F17" s="1" t="n">
         <v>1999</v>
       </c>
-      <c r="G17" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>57</v>
+      <c r="G17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="n">
         <v>1989</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>58</v>
+      <c r="B18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="D18" s="10" t="n">
         <v>390</v>
       </c>
-      <c r="G18" s="5" t="s">
-        <v>59</v>
+      <c r="G18" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2275,59 +2537,59 @@
         <v>2011</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D19" s="16" t="n">
         <v>396</v>
       </c>
-      <c r="G19" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>62</v>
+      <c r="G19" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="n">
         <v>2011</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>64</v>
+      <c r="B20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>68</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>408</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>66</v>
+      <c r="G20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="n">
         <v>2018</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>68</v>
+      <c r="B21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>72</v>
       </c>
       <c r="D21" s="10" t="n">
         <v>242</v>
       </c>
-      <c r="G21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>69</v>
+      <c r="G21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2335,35 +2597,43 @@
         <v>2020</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>200</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>72</v>
+      <c r="G22" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D23" s="7"/>
       <c r="G23" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="G24" s="1" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -2390,34 +2660,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -2444,12 +2714,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2473,30 +2743,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2524,879 +2794,879 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3441,677 +3711,677 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="1" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="1" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -4139,114 +4409,114 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4258,4 +4528,325 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:C52"/>
+  <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.24"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="0" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>480</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>482</v>
+      </c>
+      <c r="C14" s="0" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C15" s="0" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="0" t="s">
+        <v>484</v>
+      </c>
+      <c r="C16" s="0" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="0" t="s">
+        <v>488</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="0" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C22" s="0" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C23" s="0" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C24" s="0" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="0" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C26" s="0" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="0" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C28" s="0" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C29" s="0" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C30" s="21" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C31" s="0" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C32" s="0" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="0" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="0" t="s">
+        <v>504</v>
+      </c>
+      <c r="C35" s="0" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="0" t="s">
+        <v>506</v>
+      </c>
+      <c r="C36" s="0" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="0" t="s">
+        <v>508</v>
+      </c>
+      <c r="C37" s="0" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="0" t="s">
+        <v>510</v>
+      </c>
+      <c r="C38" s="0" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="0" t="s">
+        <v>512</v>
+      </c>
+      <c r="C39" s="0" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C40" s="0" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="0" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C43" s="0" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C44" s="0" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C45" s="0" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C46" s="0" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C47" s="0" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C48" s="0" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C49" s="0" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C50" s="0" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C51" s="0" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="0" t="s">
+        <v>525</v>
+      </c>
+      <c r="C52" s="0" t="s">
+        <v>526</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/Dissertation Research/Reading List.xlsx
+++ b/Dissertation Research/Reading List.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="604" uniqueCount="527">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="529">
   <si>
     <t xml:space="preserve">History</t>
   </si>
@@ -268,6 +268,12 @@
   </si>
   <si>
     <t xml:space="preserve">Three essays on Marx's Value Theory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beckert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitalism</t>
   </si>
   <si>
     <t xml:space="preserve">Best</t>
@@ -1795,7 +1801,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1878,10 +1884,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2629,11 +2631,17 @@
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>81</v>
+      </c>
       <c r="G24" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -2660,34 +2668,34 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -2714,12 +2722,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="210.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="20" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2743,30 +2751,30 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2794,879 +2802,879 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B102" s="1" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B103" s="1" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B104" s="1" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B105" s="1" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B106" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B107" s="1" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B108" s="1" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B109" s="1" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B110" s="1" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
   </sheetData>
@@ -3711,677 +3719,677 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="1" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="1" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="1" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="1" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="1" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="1" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="1" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -4409,114 +4417,114 @@
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>
@@ -4538,306 +4546,306 @@
   <dimension ref="B2:C52"/>
   <sheetFormatPr defaultColWidth="10.16015625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="19.28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.24"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>464</v>
+      <c r="B2" s="1" t="s">
+        <v>466</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>465</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>466</v>
+      <c r="B3" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>467</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>468</v>
+      <c r="B4" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>470</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>469</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>470</v>
+      <c r="B5" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="0" t="s">
-        <v>471</v>
+      <c r="C6" s="1" t="s">
+        <v>473</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="0" t="s">
-        <v>472</v>
+      <c r="C7" s="1" t="s">
+        <v>474</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>473</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>474</v>
+      <c r="B8" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>475</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>476</v>
+      <c r="B9" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>477</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>478</v>
+      <c r="B10" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>479</v>
+      <c r="B12" s="1" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>480</v>
-      </c>
-      <c r="C13" s="0" t="s">
-        <v>481</v>
+      <c r="B13" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>483</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>482</v>
-      </c>
-      <c r="C14" s="0" t="s">
-        <v>483</v>
+      <c r="B14" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>485</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="C15" s="0" t="s">
-        <v>485</v>
+      <c r="B15" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="0" t="s">
-        <v>484</v>
-      </c>
-      <c r="C16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>486</v>
       </c>
+      <c r="C16" s="1" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="0" t="s">
-        <v>487</v>
+      <c r="C17" s="1" t="s">
+        <v>489</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
-        <v>488</v>
-      </c>
-      <c r="C18" s="0" t="s">
-        <v>489</v>
+      <c r="B18" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C19" s="0" t="s">
-        <v>490</v>
+      <c r="C19" s="1" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="0" t="s">
-        <v>491</v>
+      <c r="B21" s="1" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C22" s="0" t="s">
-        <v>492</v>
+      <c r="C22" s="1" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="0" t="s">
-        <v>493</v>
+      <c r="C23" s="1" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="0" t="s">
-        <v>494</v>
+      <c r="C24" s="1" t="s">
+        <v>496</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="0" t="s">
-        <v>495</v>
+      <c r="C25" s="1" t="s">
+        <v>497</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C26" s="0" t="s">
-        <v>496</v>
+      <c r="C26" s="1" t="s">
+        <v>498</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C27" s="0" t="s">
-        <v>497</v>
+      <c r="C27" s="1" t="s">
+        <v>499</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C28" s="0" t="s">
-        <v>498</v>
+      <c r="C28" s="1" t="s">
+        <v>500</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C29" s="0" t="s">
-        <v>499</v>
+      <c r="C29" s="1" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C30" s="21" t="s">
-        <v>500</v>
+      <c r="C30" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C31" s="0" t="s">
-        <v>501</v>
+      <c r="C31" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C32" s="0" t="s">
-        <v>502</v>
+      <c r="C32" s="1" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="0" t="s">
-        <v>503</v>
+      <c r="B34" s="1" t="s">
+        <v>505</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="0" t="s">
-        <v>504</v>
-      </c>
-      <c r="C35" s="0" t="s">
-        <v>505</v>
+      <c r="B35" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="0" t="s">
-        <v>506</v>
-      </c>
-      <c r="C36" s="0" t="s">
-        <v>507</v>
+      <c r="B36" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="0" t="s">
-        <v>508</v>
-      </c>
-      <c r="C37" s="0" t="s">
-        <v>509</v>
+      <c r="B37" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="0" t="s">
-        <v>510</v>
-      </c>
-      <c r="C38" s="0" t="s">
-        <v>511</v>
+      <c r="B38" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="0" t="s">
-        <v>512</v>
-      </c>
-      <c r="C39" s="0" t="s">
-        <v>513</v>
+      <c r="B39" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C40" s="0" t="s">
-        <v>514</v>
+      <c r="C40" s="1" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="0" t="s">
-        <v>515</v>
+      <c r="B42" s="1" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C43" s="0" t="s">
-        <v>516</v>
+      <c r="C43" s="1" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C44" s="0" t="s">
-        <v>517</v>
+      <c r="C44" s="1" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C45" s="0" t="s">
-        <v>518</v>
+      <c r="C45" s="1" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C46" s="0" t="s">
-        <v>519</v>
+      <c r="C46" s="1" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C47" s="0" t="s">
-        <v>520</v>
+      <c r="C47" s="1" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C48" s="0" t="s">
-        <v>521</v>
+      <c r="C48" s="1" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C49" s="0" t="s">
-        <v>522</v>
+      <c r="C49" s="1" t="s">
+        <v>524</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C50" s="0" t="s">
-        <v>523</v>
+      <c r="C50" s="1" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C51" s="0" t="s">
-        <v>524</v>
+      <c r="C51" s="1" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="0" t="s">
-        <v>525</v>
-      </c>
-      <c r="C52" s="0" t="s">
-        <v>526</v>
+      <c r="B52" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>528</v>
       </c>
     </row>
   </sheetData>

--- a/Dissertation Research/Reading List.xlsx
+++ b/Dissertation Research/Reading List.xlsx
@@ -2448,10 +2448,10 @@
       <c r="D13" s="10" t="n">
         <v>640</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="H13" s="2" t="s">
+      <c r="H13" s="7" t="s">
         <v>47</v>
       </c>
     </row>
